--- a/outputs/excel/northwind_unit_economics.xlsx
+++ b/outputs/excel/northwind_unit_economics.xlsx
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.6</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
